--- a/request_forms/001_resident_complaint_summary_request_form--request_forms.xlsx
+++ b/request_forms/001_resident_complaint_summary_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'maintenance_issue'}</t>
+          <t>maintenance_issue</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Maintenance Issue'}</t>
+          <t>Maintenance Issue</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'noise_complaint'}</t>
+          <t>noise_complaint</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Noise Complaint'}</t>
+          <t>Noise Complaint</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
